--- a/satisfaction_surveys/007_library_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/007_library_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro_text</t>
+          <t>page1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro_text</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to answer the questions below.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,12 +542,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>how_often_visit</t>
+          <t>page2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>how_often_visit_frequency</t>
+          <t>page3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How often do you visit the library?</t>
+          <t>What do you enjoy most about our library?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>visit_frequency</t>
+          <t>page4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Visit Frequency</t>
+          <t>Have you had any issues with our library?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>visit_frequency2</t>
+          <t>page5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Visit Frequency 2</t>
+          <t>Why do you visit the library?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>visit_frequency3</t>
+          <t>page6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Visit Frequency 3</t>
+          <t>How satisfied are you with our library?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>page7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How satisfied are you with our library?</t>
+          <t>How often do you experience problems with our library?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>how_satisfied2</t>
+          <t>page8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How satisfied are you with our library?</t>
+          <t>What can we do to improve our library?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency</t>
+          <t>page9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How Satisfied Frequency</t>
+          <t>How likely are you to recommend our library to a friend or family member?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +726,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency2</t>
+          <t>page10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How Satisfied Frequency</t>
+          <t>How do you use our library resources?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +749,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>have_issues</t>
+          <t>page11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Have you ever had issues while visiting the library?</t>
+          <t>What do you value most when visiting our library?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +772,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>have_issues_frequency</t>
+          <t>page12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Have Issues Frequency</t>
+          <t>Page12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +795,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>have_issues_frequency2</t>
+          <t>page13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Have Issues Frequency 2</t>
+          <t>What is your favorite library service or feature?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>why_visit</t>
+          <t>page14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Why do you visit the library?</t>
+          <t>How would you rate your overall experience with our library?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +841,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>why_visit_frequency</t>
+          <t>page15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Why Visit Frequency</t>
+          <t>Any suggestions for library events or programs?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>why_visit_frequency2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Why Visit Frequency 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>how_satisfy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How Satisfied</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>have_issues2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Have Issues</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>how_satisfied_frequency2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How Satisfied Frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>have_issues3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Have Issues 3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>have_issues4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Have Issues 4</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>have_issues5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Have Issues 5</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>have_issues6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Have Issues 6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>have_issues7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Have Issues 7</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>have_issues8</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Have Issues 8</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +872,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,969 +900,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>visit_frequency_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Very often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>visit_frequency_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>visit_frequency_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>visit_frequency2_choices</t>
+          <t>page2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>visit_frequency2_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>visit_frequency2_choices</t>
+          <t>page4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>visit_frequency3_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>visit_frequency3_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>visit_frequency3_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>page6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Very often</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency_choices</t>
+          <t>page7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency2_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency2_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>articles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Articles</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>how_satisfied_frequency2_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>have_issues_choices</t>
+          <t>page10_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>have_issues_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>quiet_and_relaxing_atmosphere</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Quiet and relaxing atmosphere</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>have_issues_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>availability_of_resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Availability of resources</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>have_issues_frequency_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>knowledgeable_staff</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Knowledgeable staff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>have_issues_frequency_choices</t>
+          <t>page11_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>have_issues_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>have_issues_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>have_issues_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>have_issues_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>why_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>why_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>why_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>why_visit_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>why_visit_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>why_visit_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>have_issues2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>have_issues2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>have_issues2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>how_satisfied_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>how_satisfied_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>how_satisfied_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>have_issues3_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>have_issues3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>have_issues3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>have_issues4_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>have_issues4_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>have_issues4_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>have_issues5_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>have_issues5_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>have_issues5_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>have_issues6_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>have_issues6_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>have_issues6_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>have_issues7_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>have_issues7_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>have_issues7_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>have_issues8_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>have_issues8_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>have_issues8_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
